--- a/artfynd/A 52448-2024 artfynd.xlsx
+++ b/artfynd/A 52448-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121231601</v>
+        <v>121231575</v>
       </c>
       <c r="B2" t="n">
-        <v>57364</v>
+        <v>5169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långkärr, Sanda, Tosterön, Srm</t>
+          <t>Långkärr, Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613283</v>
+        <v>613285</v>
       </c>
       <c r="R2" t="n">
-        <v>6589665</v>
+        <v>6589604</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +776,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,7 +812,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121231575</v>
+        <v>121231567</v>
       </c>
       <c r="B3" t="n">
         <v>5169</v>
@@ -837,7 +857,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613285</v>
+        <v>613301</v>
       </c>
       <c r="R3" t="n">
         <v>6589604</v>
@@ -872,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121231593</v>
+        <v>121231656</v>
       </c>
       <c r="B4" t="n">
-        <v>57364</v>
+        <v>5189</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,20 +961,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -965,16 +985,16 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långkärr, Sanda, Tosterön, Srm</t>
+          <t>Långkärr, Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613300</v>
+        <v>613284</v>
       </c>
       <c r="R4" t="n">
         <v>6589635</v>
@@ -1009,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,10 +1066,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121231656</v>
+        <v>121231593</v>
       </c>
       <c r="B5" t="n">
-        <v>5189</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,20 +1078,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,16 +1102,16 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långkärr, Långkärr, Srm</t>
+          <t>Långkärr, Sanda, Tosterön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613284</v>
+        <v>613300</v>
       </c>
       <c r="R5" t="n">
         <v>6589635</v>
@@ -1126,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121231567</v>
+        <v>121231601</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,43 +1195,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långkärr, Långkärr, Srm</t>
+          <t>Långkärr, Sanda, Tosterön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613301</v>
+        <v>613283</v>
       </c>
       <c r="R6" t="n">
-        <v>6589604</v>
+        <v>6589665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1263,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1273,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,26 +1284,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1303,7 +1303,7 @@
         <v>121231803</v>
       </c>
       <c r="B7" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 52448-2024 artfynd.xlsx
+++ b/artfynd/A 52448-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121231575</v>
+        <v>121231567</v>
       </c>
       <c r="B2" t="n">
         <v>5169</v>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613285</v>
+        <v>613301</v>
       </c>
       <c r="R2" t="n">
         <v>6589604</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121231567</v>
+        <v>121231601</v>
       </c>
       <c r="B3" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,43 +824,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långkärr, Långkärr, Srm</t>
+          <t>Långkärr, Sanda, Tosterön, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613301</v>
+        <v>613283</v>
       </c>
       <c r="R3" t="n">
-        <v>6589604</v>
+        <v>6589665</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,26 +913,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -949,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121231656</v>
+        <v>121231593</v>
       </c>
       <c r="B4" t="n">
-        <v>5189</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,20 +941,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -985,16 +965,16 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långkärr, Långkärr, Srm</t>
+          <t>Långkärr, Sanda, Tosterön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613284</v>
+        <v>613300</v>
       </c>
       <c r="R4" t="n">
         <v>6589635</v>
@@ -1029,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1066,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121231593</v>
+        <v>121231575</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1078,43 +1058,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långkärr, Sanda, Tosterön, Srm</t>
+          <t>Långkärr, Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613300</v>
+        <v>613285</v>
       </c>
       <c r="R5" t="n">
-        <v>6589635</v>
+        <v>6589604</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,6 +1147,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1183,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121231601</v>
+        <v>121231656</v>
       </c>
       <c r="B6" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,20 +1195,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1219,19 +1219,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långkärr, Sanda, Tosterön, Srm</t>
+          <t>Långkärr, Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613283</v>
+        <v>613284</v>
       </c>
       <c r="R6" t="n">
-        <v>6589665</v>
+        <v>6589635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 52448-2024 artfynd.xlsx
+++ b/artfynd/A 52448-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121231567</v>
+        <v>121231593</v>
       </c>
       <c r="B2" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långkärr, Långkärr, Srm</t>
+          <t>Långkärr, Sanda, Tosterön, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613301</v>
+        <v>613300</v>
       </c>
       <c r="R2" t="n">
-        <v>6589604</v>
+        <v>6589635</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,26 +776,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121231601</v>
+        <v>121231575</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>5169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,43 +804,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långkärr, Sanda, Tosterön, Srm</t>
+          <t>Långkärr, Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613283</v>
+        <v>613285</v>
       </c>
       <c r="R3" t="n">
-        <v>6589665</v>
+        <v>6589604</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,6 +893,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121231593</v>
+        <v>121231656</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,20 +941,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -965,16 +965,16 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långkärr, Sanda, Tosterön, Srm</t>
+          <t>Långkärr, Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613300</v>
+        <v>613284</v>
       </c>
       <c r="R4" t="n">
         <v>6589635</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121231575</v>
+        <v>121231601</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,43 +1058,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långkärr, Långkärr, Srm</t>
+          <t>Långkärr, Sanda, Tosterön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613285</v>
+        <v>613283</v>
       </c>
       <c r="R5" t="n">
-        <v>6589604</v>
+        <v>6589665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,26 +1147,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1183,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121231656</v>
+        <v>121231567</v>
       </c>
       <c r="B6" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1199,21 +1179,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1228,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613284</v>
+        <v>613301</v>
       </c>
       <c r="R6" t="n">
-        <v>6589635</v>
+        <v>6589604</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1263,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1273,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,6 +1264,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 52448-2024 artfynd.xlsx
+++ b/artfynd/A 52448-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121231575</v>
+        <v>121231601</v>
       </c>
       <c r="B3" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,43 +804,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långkärr, Långkärr, Srm</t>
+          <t>Långkärr, Sanda, Tosterön, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613285</v>
+        <v>613283</v>
       </c>
       <c r="R3" t="n">
-        <v>6589604</v>
+        <v>6589665</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,26 +893,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -929,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121231656</v>
+        <v>121231575</v>
       </c>
       <c r="B4" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613284</v>
+        <v>613285</v>
       </c>
       <c r="R4" t="n">
-        <v>6589635</v>
+        <v>6589604</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,6 +1010,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121231601</v>
+        <v>121231656</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,20 +1058,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,19 +1082,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långkärr, Sanda, Tosterön, Srm</t>
+          <t>Långkärr, Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613283</v>
+        <v>613284</v>
       </c>
       <c r="R5" t="n">
-        <v>6589665</v>
+        <v>6589635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 52448-2024 artfynd.xlsx
+++ b/artfynd/A 52448-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121231593</v>
+        <v>121231575</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>5172</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långkärr, Sanda, Tosterön, Srm</t>
+          <t>Långkärr, Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613300</v>
+        <v>613285</v>
       </c>
       <c r="R2" t="n">
-        <v>6589635</v>
+        <v>6589604</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +776,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -795,7 +815,7 @@
         <v>121231601</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121231575</v>
+        <v>121231593</v>
       </c>
       <c r="B4" t="n">
-        <v>5169</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,43 +941,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långkärr, Långkärr, Srm</t>
+          <t>Långkärr, Sanda, Tosterön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613285</v>
+        <v>613300</v>
       </c>
       <c r="R4" t="n">
-        <v>6589604</v>
+        <v>6589635</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,26 +1030,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1049,7 +1049,7 @@
         <v>121231656</v>
       </c>
       <c r="B5" t="n">
-        <v>5189</v>
+        <v>5192</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>121231567</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>5172</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>121231803</v>
       </c>
       <c r="B7" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 52448-2024 artfynd.xlsx
+++ b/artfynd/A 52448-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121231575</v>
+        <v>121231656</v>
       </c>
       <c r="B2" t="n">
-        <v>5172</v>
+        <v>5192</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613285</v>
+        <v>613284</v>
       </c>
       <c r="R2" t="n">
-        <v>6589604</v>
+        <v>6589635</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,26 +776,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -929,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121231593</v>
+        <v>121231575</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>5172</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,43 +921,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långkärr, Sanda, Tosterön, Srm</t>
+          <t>Långkärr, Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613300</v>
+        <v>613285</v>
       </c>
       <c r="R4" t="n">
-        <v>6589635</v>
+        <v>6589604</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,6 +1010,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121231656</v>
+        <v>121231567</v>
       </c>
       <c r="B5" t="n">
-        <v>5192</v>
+        <v>5172</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,21 +1062,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613284</v>
+        <v>613301</v>
       </c>
       <c r="R5" t="n">
-        <v>6589635</v>
+        <v>6589604</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,6 +1147,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1163,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121231567</v>
+        <v>121231593</v>
       </c>
       <c r="B6" t="n">
-        <v>5172</v>
+        <v>57370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,43 +1195,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långkärr, Långkärr, Srm</t>
+          <t>Långkärr, Sanda, Tosterön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613301</v>
+        <v>613300</v>
       </c>
       <c r="R6" t="n">
-        <v>6589604</v>
+        <v>6589635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1263,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1273,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,26 +1284,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 52448-2024 artfynd.xlsx
+++ b/artfynd/A 52448-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121231656</v>
+        <v>121231593</v>
       </c>
       <c r="B2" t="n">
-        <v>5192</v>
+        <v>57371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,16 +711,16 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långkärr, Långkärr, Srm</t>
+          <t>Långkärr, Sanda, Tosterön, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613284</v>
+        <v>613300</v>
       </c>
       <c r="R2" t="n">
         <v>6589635</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121231601</v>
+        <v>121231656</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>5192</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,20 +804,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,19 +828,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långkärr, Sanda, Tosterön, Srm</t>
+          <t>Långkärr, Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613283</v>
+        <v>613284</v>
       </c>
       <c r="R3" t="n">
-        <v>6589665</v>
+        <v>6589635</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121231575</v>
+        <v>121231601</v>
       </c>
       <c r="B4" t="n">
-        <v>5172</v>
+        <v>57371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,43 +921,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långkärr, Långkärr, Srm</t>
+          <t>Långkärr, Sanda, Tosterön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613285</v>
+        <v>613283</v>
       </c>
       <c r="R4" t="n">
-        <v>6589604</v>
+        <v>6589665</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,26 +1010,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1046,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121231567</v>
+        <v>121231575</v>
       </c>
       <c r="B5" t="n">
         <v>5172</v>
@@ -1091,7 +1071,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613301</v>
+        <v>613285</v>
       </c>
       <c r="R5" t="n">
         <v>6589604</v>
@@ -1126,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121231593</v>
+        <v>121231567</v>
       </c>
       <c r="B6" t="n">
-        <v>57370</v>
+        <v>5172</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,43 +1175,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långkärr, Sanda, Tosterön, Srm</t>
+          <t>Långkärr, Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613300</v>
+        <v>613301</v>
       </c>
       <c r="R6" t="n">
-        <v>6589635</v>
+        <v>6589604</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1263,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1273,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,6 +1264,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1303,7 +1303,7 @@
         <v>121231803</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 52448-2024 artfynd.xlsx
+++ b/artfynd/A 52448-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121231593</v>
+        <v>121231567</v>
       </c>
       <c r="B2" t="n">
-        <v>57371</v>
+        <v>5172</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långkärr, Sanda, Tosterön, Srm</t>
+          <t>Långkärr, Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613300</v>
+        <v>613301</v>
       </c>
       <c r="R2" t="n">
-        <v>6589635</v>
+        <v>6589604</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +776,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121231656</v>
+        <v>121231575</v>
       </c>
       <c r="B3" t="n">
-        <v>5192</v>
+        <v>5172</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +828,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613284</v>
+        <v>613285</v>
       </c>
       <c r="R3" t="n">
-        <v>6589635</v>
+        <v>6589604</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,6 +913,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121231601</v>
+        <v>121231593</v>
       </c>
       <c r="B4" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613283</v>
+        <v>613300</v>
       </c>
       <c r="R4" t="n">
-        <v>6589665</v>
+        <v>6589635</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1066,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121231575</v>
+        <v>121231656</v>
       </c>
       <c r="B5" t="n">
-        <v>5172</v>
+        <v>5192</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1082,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1111,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613285</v>
+        <v>613284</v>
       </c>
       <c r="R5" t="n">
-        <v>6589604</v>
+        <v>6589635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,26 +1167,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1163,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121231567</v>
+        <v>121231601</v>
       </c>
       <c r="B6" t="n">
-        <v>5172</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,43 +1195,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långkärr, Långkärr, Srm</t>
+          <t>Långkärr, Sanda, Tosterön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613301</v>
+        <v>613283</v>
       </c>
       <c r="R6" t="n">
-        <v>6589604</v>
+        <v>6589665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1263,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1273,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,26 +1284,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1303,7 +1303,7 @@
         <v>121231803</v>
       </c>
       <c r="B7" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 52448-2024 artfynd.xlsx
+++ b/artfynd/A 52448-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121231567</v>
+        <v>121231656</v>
       </c>
       <c r="B2" t="n">
-        <v>5172</v>
+        <v>5192</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613301</v>
+        <v>613284</v>
       </c>
       <c r="R2" t="n">
-        <v>6589604</v>
+        <v>6589635</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,26 +776,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -949,7 +929,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121231593</v>
+        <v>121231601</v>
       </c>
       <c r="B4" t="n">
         <v>57372</v>
@@ -994,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613300</v>
+        <v>613283</v>
       </c>
       <c r="R4" t="n">
-        <v>6589635</v>
+        <v>6589665</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1066,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121231656</v>
+        <v>121231567</v>
       </c>
       <c r="B5" t="n">
-        <v>5192</v>
+        <v>5172</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,21 +1062,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1111,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613284</v>
+        <v>613301</v>
       </c>
       <c r="R5" t="n">
-        <v>6589635</v>
+        <v>6589604</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,6 +1147,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1183,7 +1183,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121231601</v>
+        <v>121231593</v>
       </c>
       <c r="B6" t="n">
         <v>57372</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613283</v>
+        <v>613300</v>
       </c>
       <c r="R6" t="n">
-        <v>6589665</v>
+        <v>6589635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 52448-2024 artfynd.xlsx
+++ b/artfynd/A 52448-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121231656</v>
+        <v>121231601</v>
       </c>
       <c r="B2" t="n">
-        <v>5192</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långkärr, Långkärr, Srm</t>
+          <t>Långkärr, Sanda, Tosterön, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613284</v>
+        <v>613283</v>
       </c>
       <c r="R2" t="n">
-        <v>6589635</v>
+        <v>6589665</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121231575</v>
+        <v>121231656</v>
       </c>
       <c r="B3" t="n">
-        <v>5172</v>
+        <v>5192</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613285</v>
+        <v>613284</v>
       </c>
       <c r="R3" t="n">
-        <v>6589604</v>
+        <v>6589635</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,26 +893,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -929,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121231601</v>
+        <v>121231567</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,43 +921,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långkärr, Sanda, Tosterön, Srm</t>
+          <t>Långkärr, Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613283</v>
+        <v>613301</v>
       </c>
       <c r="R4" t="n">
-        <v>6589665</v>
+        <v>6589604</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,6 +1010,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121231567</v>
+        <v>121231593</v>
       </c>
       <c r="B5" t="n">
-        <v>5172</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,43 +1058,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långkärr, Långkärr, Srm</t>
+          <t>Långkärr, Sanda, Tosterön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613301</v>
+        <v>613300</v>
       </c>
       <c r="R5" t="n">
-        <v>6589604</v>
+        <v>6589635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,26 +1147,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1183,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121231593</v>
+        <v>121231575</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,43 +1175,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långkärr, Sanda, Tosterön, Srm</t>
+          <t>Långkärr, Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613300</v>
+        <v>613285</v>
       </c>
       <c r="R6" t="n">
-        <v>6589635</v>
+        <v>6589604</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1263,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1273,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,6 +1264,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
